--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,15 +1693,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="A49" t="n">
+        <v>77</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1.5</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
@@ -1712,17 +1708,645 @@
       <c r="E49" t="n">
         <v>-18</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-18.37</t>
-        </is>
+      <c r="F49" t="n">
+        <v>-18.37</v>
       </c>
       <c r="G49" t="n">
         <v>0.370000000000001</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>56</t>
+      <c r="H49" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>72</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H50" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>72</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H51" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>72</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-16</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>72</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-16.26</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.260000000000002</v>
+      </c>
+      <c r="H53" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>72</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H54" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>72</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="H55" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>72</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H56" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>72</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="H57" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>71</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-14.06</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9399999999999995</v>
+      </c>
+      <c r="H58" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>71</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>71</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G60" t="n">
+        <v>11</v>
+      </c>
+      <c r="H60" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>71</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-23.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.359999999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>71</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-16.12</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5799999999999983</v>
+      </c>
+      <c r="H62" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>71</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-14.59</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H63" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>71</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-22</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-21.85</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1499999999999986</v>
+      </c>
+      <c r="H64" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>71</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>66</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,15 +2317,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
+      <c r="A73" t="n">
+        <v>66</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1.54</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
@@ -2336,17 +2332,229 @@
       <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
+      <c r="F73" t="n">
+        <v>-0.34</v>
       </c>
       <c r="G73" t="n">
         <v>0.34</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>50</t>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H74" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-10.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H75" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-22.59</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H76" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>71</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-12.59</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H77" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.7100000000000009</v>
+      </c>
+      <c r="H78" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>71</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-12.37</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.630000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-13.91</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-15.60</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>75</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="10">
   <si>
     <t>Age</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Feminine</t>
-  </si>
-  <si>
-    <t>1.60</t>
   </si>
 </sst>
 </file>
@@ -117,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -151,6 +148,9 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -457,7 +457,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -466,7 +466,7 @@
     <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -483,7 +483,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2969,11 +2969,11 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
-      <c r="A105" s="7">
+      <c r="A105" s="4">
         <v>60</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>10</v>
+      <c r="B105" s="5">
+        <v>1.6</v>
       </c>
       <c r="C105" s="6"/>
       <c r="D105" s="6" t="s">
@@ -2982,14 +2982,206 @@
       <c r="E105" s="5">
         <v>1.5</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="5">
         <v>2.09</v>
       </c>
       <c r="G105" s="5">
         <v>0.5899999999999999</v>
       </c>
-      <c r="H105" s="7">
+      <c r="H105" s="4">
         <v>62</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+      <c r="A106" s="4">
+        <v>76</v>
+      </c>
+      <c r="B106" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="4">
+        <v>-20</v>
+      </c>
+      <c r="F106" s="5">
+        <v>-21.35</v>
+      </c>
+      <c r="G106" s="5">
+        <v>1.350000000000001</v>
+      </c>
+      <c r="H106" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+      <c r="A107" s="4">
+        <v>76</v>
+      </c>
+      <c r="B107" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="5">
+        <v>-18.5</v>
+      </c>
+      <c r="F107" s="5">
+        <v>-18.1</v>
+      </c>
+      <c r="G107" s="5">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="H107" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+      <c r="A108" s="4">
+        <v>76</v>
+      </c>
+      <c r="B108" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="4">
+        <v>-9</v>
+      </c>
+      <c r="F108" s="5">
+        <v>-8.73</v>
+      </c>
+      <c r="G108" s="5">
+        <v>0.2699999999999996</v>
+      </c>
+      <c r="H108" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+      <c r="A109" s="4">
+        <v>76</v>
+      </c>
+      <c r="B109" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F109" s="5">
+        <v>-7.81</v>
+      </c>
+      <c r="G109" s="5">
+        <v>0.1900000000000004</v>
+      </c>
+      <c r="H109" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+      <c r="A110" s="4">
+        <v>76</v>
+      </c>
+      <c r="B110" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="4">
+        <v>-15</v>
+      </c>
+      <c r="F110" s="5">
+        <v>-14.1</v>
+      </c>
+      <c r="G110" s="5">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="H110" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+      <c r="A111" s="4">
+        <v>76</v>
+      </c>
+      <c r="B111" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F111" s="5">
+        <v>-13.14</v>
+      </c>
+      <c r="G111" s="5">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="H111" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+      <c r="A112" s="4">
+        <v>76</v>
+      </c>
+      <c r="B112" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F112" s="5">
+        <v>-6.97</v>
+      </c>
+      <c r="G112" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="H112" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+      <c r="A113" s="7">
+        <v>76</v>
+      </c>
+      <c r="B113" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F113" s="8">
+        <v>-5.16</v>
+      </c>
+      <c r="G113" s="5">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="H113" s="7">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="10">
   <si>
     <t>Age</t>
   </si>
@@ -457,7 +457,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3161,10 +3161,10 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
-      <c r="A113" s="7">
+      <c r="A113" s="4">
         <v>76</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="5">
         <v>1.52</v>
       </c>
       <c r="C113" s="6"/>
@@ -3174,14 +3174,206 @@
       <c r="E113" s="4">
         <v>-6</v>
       </c>
-      <c r="F113" s="8">
+      <c r="F113" s="5">
         <v>-5.16</v>
       </c>
       <c r="G113" s="5">
         <v>0.8399999999999999</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H113" s="4">
         <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+      <c r="A114" s="4">
+        <v>73</v>
+      </c>
+      <c r="B114" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="4">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="G114" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="H114" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+      <c r="A115" s="4">
+        <v>73</v>
+      </c>
+      <c r="B115" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="4">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5">
+        <v>-1.22</v>
+      </c>
+      <c r="G115" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="H115" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+      <c r="A116" s="4">
+        <v>73</v>
+      </c>
+      <c r="B116" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="4">
+        <v>-20</v>
+      </c>
+      <c r="F116" s="5">
+        <v>-21.75</v>
+      </c>
+      <c r="G116" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H116" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+      <c r="A117" s="4">
+        <v>73</v>
+      </c>
+      <c r="B117" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="4">
+        <v>-17</v>
+      </c>
+      <c r="F117" s="5">
+        <v>-20.4</v>
+      </c>
+      <c r="G117" s="5">
+        <v>3.04</v>
+      </c>
+      <c r="H117" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+      <c r="A118" s="4">
+        <v>76</v>
+      </c>
+      <c r="B118" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="4">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="G118" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="H118" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+      <c r="A119" s="4">
+        <v>76</v>
+      </c>
+      <c r="B119" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="4">
+        <v>0</v>
+      </c>
+      <c r="F119" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G119" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="H119" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+      <c r="A120" s="4">
+        <v>76</v>
+      </c>
+      <c r="B120" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="4">
+        <v>-16</v>
+      </c>
+      <c r="F120" s="5">
+        <v>-20.72</v>
+      </c>
+      <c r="G120" s="5">
+        <v>4.72</v>
+      </c>
+      <c r="H120" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+      <c r="A121" s="7">
+        <v>73</v>
+      </c>
+      <c r="B121" s="8">
+        <v>1.66</v>
+      </c>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="4">
+        <v>-17</v>
+      </c>
+      <c r="F121" s="8">
+        <v>-18.43</v>
+      </c>
+      <c r="G121" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="H121" s="7">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="10">
   <si>
     <t>Age</t>
   </si>
@@ -457,7 +457,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3353,10 +3353,10 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
-      <c r="A121" s="7">
+      <c r="A121" s="4">
         <v>73</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="5">
         <v>1.66</v>
       </c>
       <c r="C121" s="6"/>
@@ -3366,14 +3366,206 @@
       <c r="E121" s="4">
         <v>-17</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="5">
         <v>-18.43</v>
       </c>
       <c r="G121" s="5">
         <v>1.43</v>
       </c>
-      <c r="H121" s="7">
+      <c r="H121" s="4">
         <v>68</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+      <c r="A122" s="4">
+        <v>82</v>
+      </c>
+      <c r="B122" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" s="4">
+        <v>-31</v>
+      </c>
+      <c r="F122" s="5">
+        <v>-32.91</v>
+      </c>
+      <c r="G122" s="5">
+        <v>1.91</v>
+      </c>
+      <c r="H122" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+      <c r="A123" s="4">
+        <v>82</v>
+      </c>
+      <c r="B123" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" s="4">
+        <v>-27</v>
+      </c>
+      <c r="F123" s="5">
+        <v>-30.86</v>
+      </c>
+      <c r="G123" s="5">
+        <v>3.86</v>
+      </c>
+      <c r="H123" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+      <c r="A124" s="4">
+        <v>82</v>
+      </c>
+      <c r="B124" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="4">
+        <v>-32</v>
+      </c>
+      <c r="F124" s="5">
+        <v>-30.29</v>
+      </c>
+      <c r="G124" s="5">
+        <v>1.71</v>
+      </c>
+      <c r="H124" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+      <c r="A125" s="4">
+        <v>82</v>
+      </c>
+      <c r="B125" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="4">
+        <v>-40</v>
+      </c>
+      <c r="F125" s="5">
+        <v>-38.72</v>
+      </c>
+      <c r="G125" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="H125" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+      <c r="A126" s="4">
+        <v>82</v>
+      </c>
+      <c r="B126" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="4">
+        <v>-30</v>
+      </c>
+      <c r="F126" s="5">
+        <v>-34.83</v>
+      </c>
+      <c r="G126" s="5">
+        <v>4.83</v>
+      </c>
+      <c r="H126" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+      <c r="A127" s="4">
+        <v>82</v>
+      </c>
+      <c r="B127" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="4">
+        <v>-30</v>
+      </c>
+      <c r="F127" s="5">
+        <v>-27.62</v>
+      </c>
+      <c r="G127" s="5">
+        <v>2.38</v>
+      </c>
+      <c r="H127" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+      <c r="A128" s="4">
+        <v>82</v>
+      </c>
+      <c r="B128" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="4">
+        <v>-31</v>
+      </c>
+      <c r="F128" s="5">
+        <v>-28.73</v>
+      </c>
+      <c r="G128" s="5">
+        <v>2.27</v>
+      </c>
+      <c r="H128" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+      <c r="A129" s="7">
+        <v>82</v>
+      </c>
+      <c r="B129" s="8">
+        <v>1.69</v>
+      </c>
+      <c r="C129" s="6"/>
+      <c r="D129" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="4">
+        <v>-42</v>
+      </c>
+      <c r="F129" s="8">
+        <v>-48.52</v>
+      </c>
+      <c r="G129" s="5">
+        <v>6.52</v>
+      </c>
+      <c r="H129" s="7">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4189,15 +4189,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
+      <c r="A145" t="n">
+        <v>62</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1.63</v>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
@@ -4208,17 +4204,437 @@
       <c r="E145" t="n">
         <v>-10</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-10.67</t>
-        </is>
+      <c r="F145" t="n">
+        <v>-10.67</v>
       </c>
       <c r="G145" t="n">
         <v>0.6699999999999999</v>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>58</t>
+      <c r="H145" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>79</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="H146" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>79</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-17.48</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H147" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>79</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-24.21</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.2100000000000009</v>
+      </c>
+      <c r="H148" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>79</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.01000000000000156</v>
+      </c>
+      <c r="H149" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>79</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-19.96</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3.960000000000001</v>
+      </c>
+      <c r="H150" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>79</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.949999999999999</v>
+      </c>
+      <c r="H151" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>79</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-29.48</v>
+      </c>
+      <c r="G152" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H152" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>79</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-23.19</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3.190000000000001</v>
+      </c>
+      <c r="H153" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>70</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H154" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>70</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F155" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H155" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>70</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="H156" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>70</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.3299999999999983</v>
+      </c>
+      <c r="H157" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>70</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H158" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>70</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-7.79</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H159" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>70</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F160" t="n">
+        <v>-20.68</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="H160" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-21.89</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1.890000000000001</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>84</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/back_scratch_utentes.xlsx
+++ b/tabelas_utentes/back_scratch_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4605,15 +4605,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
+      <c r="A161" t="n">
+        <v>70</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1.64</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
@@ -4624,17 +4620,229 @@
       <c r="E161" t="n">
         <v>-20</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-21.89</t>
-        </is>
+      <c r="F161" t="n">
+        <v>-21.89</v>
       </c>
       <c r="G161" t="n">
         <v>1.890000000000001</v>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>84</t>
+      <c r="H161" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>70</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>-29</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-29.03</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="H162" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>70</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H163" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>70</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="H164" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>70</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-16.85</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.8500000000000014</v>
+      </c>
+      <c r="H165" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>70</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H166" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>70</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H167" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>70</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F168" t="n">
+        <v>-15.25</v>
+      </c>
+      <c r="G168" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H168" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-25.39</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>69</t>
         </is>
       </c>
     </row>
